--- a/Data/Tables/__enums__.xlsx
+++ b/Data/Tables/__enums__.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangyang/Documents/IAAAProject/MiniTemplate/Datas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangyang/Documents/Deliverables/AdPlayerDemo/Data/Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CBE5864-FD45-8147-8D93-123A1F3DA6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9F2839-DFCC-3441-9CC8-30A30CAF4C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6620" windowWidth="29280" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="1260" windowWidth="29160" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -79,39 +79,31 @@
     <t>注释</t>
   </si>
   <si>
-    <t>RED</t>
+    <t>Card.CardType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>红</t>
+    <t>普通牌</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>GREEN</t>
+    <t>特殊牌</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BLUE</t>
+    <t>正常手牌，没有特殊功能</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>WHITE</t>
+    <t>会产生特殊功能</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>绿</t>
+    <t>NORMAL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>蓝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GridTileType</t>
+    <t>SPECIAL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -486,9 +478,9 @@
     <col min="6" max="6" width="9.33203125" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
     <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" customWidth="1"/>
+    <col min="9" max="9" width="7.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.1640625" customWidth="1"/>
-    <col min="11" max="11" width="15.1640625" customWidth="1"/>
+    <col min="11" max="11" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -579,56 +571,43 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="b">
-        <v>1</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="D4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J4">
         <v>1</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="H5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J5">
         <v>2</v>
       </c>
+      <c r="K5" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="H6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="H7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
